--- a/docs/direct-campaign.xlsx
+++ b/docs/direct-campaign.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="454">
   <si>
     <t xml:space="preserve">Параметр</t>
   </si>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">Комиссия до 50 000 ₽</t>
   </si>
   <si>
-    <t xml:space="preserve">Сравним объявления, проверим историю и проходимость в РФ. Расчёт цены онлайн.</t>
+    <t xml:space="preserve">Сравним объявления, проверим историю и проходимость в РФ. Цены онлайн в рублях.</t>
   </si>
   <si>
     <t xml:space="preserve">Kia-K5</t>
@@ -1346,13 +1346,13 @@
     <t xml:space="preserve">Быстрая ссылка</t>
   </si>
   <si>
-    <t xml:space="preserve">Калькулятор стоимости</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пошлина, утильсбор и сборы по действующим ставкам</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#calc</t>
+    <t xml:space="preserve">Объявления онлайн</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Свежие машины из Кореи и Китая с ценой в рублях</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#terminal</t>
   </si>
   <si>
     <t xml:space="preserve">Как машина поедет к вам</t>
@@ -1373,13 +1373,10 @@
     <t xml:space="preserve">#vydachi</t>
   </si>
   <si>
-    <t xml:space="preserve">Подбор под бюджет</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оставьте заявку — пришлём варианты</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#podbor</t>
+    <t xml:space="preserve">Проверьте нас</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Юрлицо, офис во Владивостоке, договор</t>
   </si>
   <si>
     <t xml:space="preserve">Уточнение</t>
@@ -2073,7 +2070,7 @@
       </c>
       <c r="I2" s="7" t="n">
         <f aca="false">LEN(H2)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>53</v>
@@ -2165,7 +2162,7 @@
       </c>
       <c r="I4" s="7" t="n">
         <f aca="false">LEN(H4)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J4" s="6" t="s">
         <v>61</v>
@@ -2257,7 +2254,7 @@
       </c>
       <c r="I6" s="7" t="n">
         <f aca="false">LEN(H6)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>66</v>
@@ -2349,7 +2346,7 @@
       </c>
       <c r="I8" s="7" t="n">
         <f aca="false">LEN(H8)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>71</v>
@@ -2441,7 +2438,7 @@
       </c>
       <c r="I10" s="7" t="n">
         <f aca="false">LEN(H10)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>76</v>
@@ -2533,7 +2530,7 @@
       </c>
       <c r="I12" s="7" t="n">
         <f aca="false">LEN(H12)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>81</v>
@@ -2625,7 +2622,7 @@
       </c>
       <c r="I14" s="7" t="n">
         <f aca="false">LEN(H14)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>86</v>
@@ -2717,7 +2714,7 @@
       </c>
       <c r="I16" s="7" t="n">
         <f aca="false">LEN(H16)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>91</v>
@@ -2809,7 +2806,7 @@
       </c>
       <c r="I18" s="7" t="n">
         <f aca="false">LEN(H18)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>96</v>
@@ -2901,7 +2898,7 @@
       </c>
       <c r="I20" s="7" t="n">
         <f aca="false">LEN(H20)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>101</v>
@@ -2993,7 +2990,7 @@
       </c>
       <c r="I22" s="7" t="n">
         <f aca="false">LEN(H22)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>106</v>
@@ -3085,7 +3082,7 @@
       </c>
       <c r="I24" s="7" t="n">
         <f aca="false">LEN(H24)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>112</v>
@@ -3177,7 +3174,7 @@
       </c>
       <c r="I26" s="7" t="n">
         <f aca="false">LEN(H26)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>117</v>
@@ -3269,7 +3266,7 @@
       </c>
       <c r="I28" s="7" t="n">
         <f aca="false">LEN(H28)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>122</v>
@@ -3361,7 +3358,7 @@
       </c>
       <c r="I30" s="7" t="n">
         <f aca="false">LEN(H30)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>127</v>
@@ -3453,7 +3450,7 @@
       </c>
       <c r="I32" s="7" t="n">
         <f aca="false">LEN(H32)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>132</v>
@@ -3545,7 +3542,7 @@
       </c>
       <c r="I34" s="7" t="n">
         <f aca="false">LEN(H34)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>137</v>
@@ -3637,7 +3634,7 @@
       </c>
       <c r="I36" s="7" t="n">
         <f aca="false">LEN(H36)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>142</v>
@@ -3729,7 +3726,7 @@
       </c>
       <c r="I38" s="7" t="n">
         <f aca="false">LEN(H38)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J38" s="6" t="s">
         <v>147</v>
@@ -3821,7 +3818,7 @@
       </c>
       <c r="I40" s="7" t="n">
         <f aca="false">LEN(H40)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J40" s="6" t="s">
         <v>153</v>
@@ -3909,7 +3906,7 @@
       </c>
       <c r="I42" s="7" t="n">
         <f aca="false">LEN(H42)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>157</v>
@@ -3997,7 +3994,7 @@
       </c>
       <c r="I44" s="7" t="n">
         <f aca="false">LEN(H44)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J44" s="6" t="s">
         <v>161</v>
@@ -6894,21 +6891,21 @@
       </c>
       <c r="C2" s="10" t="n">
         <f aca="false">LEN(B2)</f>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>441</v>
       </c>
       <c r="E2" s="10" t="n">
         <f aca="false">LEN(D2)</f>
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>442</v>
       </c>
       <c r="G2" s="8" t="str">
         <f aca="false">Настройки!$B$2&amp;"?"&amp;Настройки!$B$3&amp;F2</f>
-        <v>https://renal-auto.asia:8443/port?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign={campaign_id}&amp;utm_content={ad_id}&amp;utm_term={keyword}#calc</v>
+        <v>https://renal-auto.asia:8443/port?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign={campaign_id}&amp;utm_content={ad_id}&amp;utm_term={keyword}#terminal</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6972,26 +6969,26 @@
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">LEN(B5)</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>450</v>
       </c>
       <c r="E5" s="10" t="n">
         <f aca="false">LEN(D5)</f>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G5" s="8" t="str">
         <f aca="false">Настройки!$B$2&amp;"?"&amp;Настройки!$B$3&amp;F5</f>
-        <v>https://renal-auto.asia:8443/port?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign={campaign_id}&amp;utm_content={ad_id}&amp;utm_term={keyword}#podbor</v>
+        <v>https://renal-auto.asia:8443/port?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign={campaign_id}&amp;utm_content={ad_id}&amp;utm_term={keyword}#vydachi</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>57</v>
@@ -7003,7 +7000,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>51</v>
@@ -7015,10 +7012,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>452</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>453</v>
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">LEN(B8)</f>
@@ -7027,10 +7024,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">LEN(B9)</f>
